--- a/图片信息.xlsx
+++ b/图片信息.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\图片灵感库\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\图片灵感库\build-inspiration-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28995" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="219">
   <si>
     <t>时间</t>
   </si>
@@ -664,6 +664,33 @@
   </si>
   <si>
     <t>https://i.pinimg.com/736x/59/0c/03/590c033145f2600ba8b43faa3f3106de.jpg</t>
+  </si>
+  <si>
+    <t>20260804203447940.jpeg</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>https://www.pinterest.com/pin/1548181186602917/</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/ea/68/58/ea685842b37ab5f334738e6b25bd7cae.jpg</t>
+  </si>
+  <si>
+    <t>spatial atmosphere</t>
+  </si>
+  <si>
+    <t>20260804203510303.jpeg</t>
+  </si>
+  <si>
+    <t>Omar M-Y</t>
+  </si>
+  <si>
+    <t>https://www.pinterest.com/pin/25684660372637592/</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/5a/f9/a0/5af9a0910676246745a53ec2a9917a85.jpg</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1628,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="25.8230088495575" style="1" customWidth="1"/>
@@ -2670,6 +2697,46 @@
       </c>
       <c r="F53" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" t="s">
+        <v>213</v>
+      </c>
+      <c r="F54" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" t="s">
+        <v>217</v>
+      </c>
+      <c r="E55" t="s">
+        <v>218</v>
+      </c>
+      <c r="F55" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
